--- a/data/Telefonia_movil.xlsx
+++ b/data/Telefonia_movil.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="60" windowWidth="16410" windowHeight="4710"/>
+    <workbookView xWindow="0" yWindow="60" windowWidth="16410" windowHeight="4710" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="SMS" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="88">
   <si>
     <t>Año</t>
   </si>
@@ -281,6 +281,9 @@
   </si>
   <si>
     <t>Ene-Mar 2024</t>
+  </si>
+  <si>
+    <t>Abr-Jun 2024</t>
   </si>
 </sst>
 </file>
@@ -1472,6 +1475,18 @@
       <c r="N46" s="7"/>
     </row>
     <row r="47" spans="1:14">
+      <c r="A47">
+        <v>2024</v>
+      </c>
+      <c r="B47">
+        <v>2</v>
+      </c>
+      <c r="C47">
+        <v>612240518</v>
+      </c>
+      <c r="D47" t="s">
+        <v>87</v>
+      </c>
       <c r="N47" s="7"/>
     </row>
   </sheetData>
@@ -2415,13 +2430,13 @@
         <v>4</v>
       </c>
       <c r="C45" s="2">
-        <v>3416387.8020000001</v>
+        <v>3413225.9220000003</v>
       </c>
       <c r="D45" s="2">
-        <v>1166789.095</v>
+        <v>1165615.9920000001</v>
       </c>
       <c r="E45" s="2">
-        <v>4583176.8969999999</v>
+        <v>4578841.9140000008</v>
       </c>
       <c r="F45" t="s">
         <v>85</v>
@@ -2435,13 +2450,13 @@
         <v>1</v>
       </c>
       <c r="C46" s="2">
-        <v>3032453.8020000001</v>
+        <v>2893507.5470000003</v>
       </c>
       <c r="D46" s="2">
-        <v>1060861.095</v>
+        <v>1068709.8870000001</v>
       </c>
       <c r="E46" s="2">
-        <v>4093314.8969999999</v>
+        <v>3962217.4340000004</v>
       </c>
       <c r="F46" t="s">
         <v>86</v>
@@ -2449,6 +2464,24 @@
       <c r="O46" s="7"/>
     </row>
     <row r="47" spans="1:15">
+      <c r="A47">
+        <v>2024</v>
+      </c>
+      <c r="B47">
+        <v>2</v>
+      </c>
+      <c r="C47" s="2">
+        <v>2709620.477</v>
+      </c>
+      <c r="D47" s="2">
+        <v>1067027.5090000001</v>
+      </c>
+      <c r="E47" s="2">
+        <v>3776647.986</v>
+      </c>
+      <c r="F47" t="s">
+        <v>87</v>
+      </c>
       <c r="O47" s="7"/>
     </row>
   </sheetData>
@@ -3410,13 +3443,13 @@
         <v>1</v>
       </c>
       <c r="C46" s="2">
-        <v>9798647.8169999998</v>
+        <v>9619808.6919999998</v>
       </c>
       <c r="D46" s="2">
-        <v>3708874.0670000003</v>
+        <v>3771708.4810000001</v>
       </c>
       <c r="E46" s="2">
-        <v>13507521.884</v>
+        <v>13391517.173</v>
       </c>
       <c r="F46" t="s">
         <v>86</v>
@@ -3424,6 +3457,24 @@
       <c r="O46" s="7"/>
     </row>
     <row r="47" spans="1:15">
+      <c r="A47">
+        <v>2024</v>
+      </c>
+      <c r="B47">
+        <v>2</v>
+      </c>
+      <c r="C47" s="2">
+        <v>8837499.6919999998</v>
+      </c>
+      <c r="D47" s="2">
+        <v>3595205.4810000001</v>
+      </c>
+      <c r="E47" s="2">
+        <v>12432705.173</v>
+      </c>
+      <c r="F47" t="s">
+        <v>87</v>
+      </c>
       <c r="O47" s="8"/>
     </row>
   </sheetData>
@@ -3433,7 +3484,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="19.42578125" bestFit="1" customWidth="1"/>
@@ -4085,6 +4136,20 @@
         <v>86</v>
       </c>
     </row>
+    <row r="47" spans="1:13">
+      <c r="A47">
+        <v>2024</v>
+      </c>
+      <c r="B47">
+        <v>2</v>
+      </c>
+      <c r="C47">
+        <v>1108472514</v>
+      </c>
+      <c r="D47" t="s">
+        <v>87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -4093,7 +4158,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N46"/>
+  <dimension ref="A1:N47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="23.28515625" customWidth="1"/>
@@ -4743,6 +4808,20 @@
         <v>86</v>
       </c>
       <c r="N46" s="3"/>
+    </row>
+    <row r="47" spans="1:14">
+      <c r="A47">
+        <v>2024</v>
+      </c>
+      <c r="B47">
+        <v>2</v>
+      </c>
+      <c r="C47" s="3">
+        <v>133.56202274294492</v>
+      </c>
+      <c r="D47" t="s">
+        <v>87</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5683,6 +5762,24 @@
       <c r="O46" s="7"/>
     </row>
     <row r="47" spans="1:15">
+      <c r="A47">
+        <v>2024</v>
+      </c>
+      <c r="B47">
+        <v>2</v>
+      </c>
+      <c r="C47">
+        <v>8397205</v>
+      </c>
+      <c r="D47">
+        <v>54421319</v>
+      </c>
+      <c r="E47">
+        <v>62818524</v>
+      </c>
+      <c r="F47" t="s">
+        <v>87</v>
+      </c>
       <c r="O47" s="7"/>
     </row>
     <row r="48" spans="1:15">
